--- a/tools/importer/reports/import-ivs-get-the-facts.report.xlsx
+++ b/tools/importer/reports/import-ivs-get-the-facts.report.xlsx
@@ -82,7 +82,7 @@
     <t>ivs-get-the-facts</t>
   </si>
   <si>
-    <t>2026-10-08T13:12:03.576Z</t>
+    <t>2026-10-12T10:07:36.323Z</t>
   </si>
   <si>
     <t>Get the facts | Stryker</t>

--- a/tools/importer/reports/import-ivs-get-the-facts.report.xlsx
+++ b/tools/importer/reports/import-ivs-get-the-facts.report.xlsx
@@ -82,7 +82,7 @@
     <t>ivs-get-the-facts</t>
   </si>
   <si>
-    <t>2026-10-12T10:07:36.323Z</t>
+    <t>2026-10-12T10:30:18.552Z</t>
   </si>
   <si>
     <t>Get the facts | Stryker</t>
